--- a/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,33</t>
+          <t>-2,68; 4,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 7,73</t>
+          <t>-2,52; 7,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,71</t>
+          <t>-3,36; 2,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 2,72</t>
+          <t>-6,6; 1,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 2,84</t>
+          <t>-5,95; 3,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,48</t>
+          <t>-5,94; 3,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,13</t>
+          <t>-3,43; 2,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,73</t>
+          <t>-3,54; 2,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,37</t>
+          <t>-3,01; 2,23</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,16; 203,91</t>
+          <t>-85,64; 254,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 270,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,05; 255,63</t>
+          <t>-75,41; 214,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 4,41</t>
+          <t>-4,85; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 2,42</t>
+          <t>-5,59; 2,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,91</t>
+          <t>-4,32; 3,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 4,82</t>
+          <t>-3,78; 4,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 2,46</t>
+          <t>-4,74; 2,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 6,85</t>
+          <t>-2,07; 6,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 3,0</t>
+          <t>-3,11; 2,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,27</t>
+          <t>-3,56; 1,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,56</t>
+          <t>-2,17; 4,08</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,87; —</t>
+          <t>-88,44; 541,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,41; 350,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 150,41</t>
+          <t>-100,0; 288,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 435,61</t>
+          <t>-59,04; 411,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,95</t>
+          <t>-3,98; 3,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 7,77</t>
+          <t>-1,61; 7,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 10,6</t>
+          <t>-0,49; 10,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 8,35</t>
+          <t>-2,41; 8,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 8,95</t>
+          <t>-2,07; 8,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 9,73</t>
+          <t>-1,64; 9,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,95</t>
+          <t>-1,54; 4,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,97</t>
+          <t>-1,13; 6,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 7,77</t>
+          <t>0,04; 7,74</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,65; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,6; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 786,45</t>
+          <t>-61,47; 590,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 1056,92</t>
+          <t>-49,98; 973,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 1478,89</t>
+          <t>-22,08; 994,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,62</t>
+          <t>-0,5; 4,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,66</t>
+          <t>-0,38; 4,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,1</t>
+          <t>0,78; 6,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,1</t>
+          <t>-3,61; 3,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,59</t>
+          <t>-4,43; 1,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 10,03</t>
+          <t>-0,66; 10,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,66</t>
+          <t>-1,53; 2,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,18</t>
+          <t>-1,53; 2,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,68</t>
+          <t>0,57; 6,5</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,49; —</t>
+          <t>-75,22; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,28; —</t>
+          <t>-12,65; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 180,41</t>
+          <t>-66,72; 163,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,18; 91,86</t>
+          <t>-79,64; 124,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 496,75</t>
+          <t>-28,3; 440,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 208,83</t>
+          <t>-52,25; 217,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 169,13</t>
+          <t>-50,56; 187,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,58; 485,6</t>
+          <t>9,46; 449,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 3,86</t>
+          <t>-6,62; 3,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 3,47</t>
+          <t>-6,87; 3,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 11,59</t>
+          <t>-1,22; 11,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 3,32</t>
+          <t>-6,86; 3,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,93</t>
+          <t>-9,33; 0,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 6,68</t>
+          <t>-4,32; 6,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 1,97</t>
+          <t>-5,26; 1,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 1,13</t>
+          <t>-5,99; 0,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,4</t>
+          <t>-0,85; 7,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,86; 496,59</t>
+          <t>-91,0; 366,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 241,61</t>
+          <t>-89,36; 287,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 753,56</t>
+          <t>-28,97; 671,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-83,54; 182,95</t>
+          <t>-83,05; 156,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,1</t>
+          <t>-100,0; 64,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 251,36</t>
+          <t>-51,08; 221,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-73,58; 74,25</t>
+          <t>-74,19; 78,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-79,9; 59,89</t>
+          <t>-82,61; 33,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 257,13</t>
+          <t>-16,32; 236,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 10,56</t>
+          <t>0,73; 11,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,33</t>
+          <t>-1,54; 5,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,25</t>
+          <t>2,55; 14,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 7,77</t>
+          <t>-2,9; 7,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,35</t>
+          <t>-5,62; 2,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 14,33</t>
+          <t>0,64; 15,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,35</t>
+          <t>0,08; 7,19</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,4</t>
+          <t>-2,61; 2,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,25; 12,5</t>
+          <t>3,16; 11,86</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-69,13; —</t>
+          <t>-67,88; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 1345,05</t>
+          <t>-24,84; 1789,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 1189,57</t>
+          <t>-18,85; 1074,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 707,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>55,26; 2079,26</t>
+          <t>83,55; 2006,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,67</t>
+          <t>-0,32; 2,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,41</t>
+          <t>-0,57; 2,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,95</t>
+          <t>1,73; 5,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,93</t>
+          <t>-1,78; 1,92</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,45</t>
+          <t>-2,83; 0,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,14</t>
+          <t>0,5; 4,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,77</t>
+          <t>-0,58; 1,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,91</t>
+          <t>-1,32; 1,01</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,56</t>
+          <t>1,69; 4,69</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 260,12</t>
+          <t>-15,44; 244,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 206,06</t>
+          <t>-26,11; 238,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>63,33; 428,27</t>
+          <t>51,56; 465,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 77,31</t>
+          <t>-40,83; 75,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-67,05; 18,58</t>
+          <t>-65,31; 20,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,97; 184,17</t>
+          <t>8,66; 192,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 85,57</t>
+          <t>-19,94; 89,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 42,92</t>
+          <t>-41,1; 50,81</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>41,18; 209,25</t>
+          <t>48,65; 212,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,09</t>
+          <t>-2,78; 4,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 7,68</t>
+          <t>-2,53; 8,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,73</t>
+          <t>-3,71; 2,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,93</t>
+          <t>-6,78; 1,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,01</t>
+          <t>-6,65; 2,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 3,18</t>
+          <t>-5,95; 3,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,3</t>
+          <t>-3,75; 2,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,84</t>
+          <t>-3,45; 2,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,23</t>
+          <t>-3,11; 2,26</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 280,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 254,2</t>
+          <t>-88,51; 206,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 270,94</t>
+          <t>-91,33; 334,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,41; 214,07</t>
+          <t>-76,67; 231,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 3,47</t>
+          <t>-4,82; 3,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,47</t>
+          <t>-5,8; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,86</t>
+          <t>-4,26; 4,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 4,74</t>
+          <t>-3,22; 4,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 2,47</t>
+          <t>-4,21; 3,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,96</t>
+          <t>-2,34; 6,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,78</t>
+          <t>-3,32; 2,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,45</t>
+          <t>-3,97; 1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 4,08</t>
+          <t>-1,86; 4,25</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,44; 541,43</t>
+          <t>-85,04; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,28; 380,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 288,11</t>
+          <t>-100,0; 319,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 411,5</t>
+          <t>-54,73; 423,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,86</t>
+          <t>-3,05; 3,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 7,48</t>
+          <t>-1,6; 7,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 10,62</t>
+          <t>-1,07; 11,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 8,37</t>
+          <t>-1,86; 8,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 8,63</t>
+          <t>-2,3; 8,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 9,86</t>
+          <t>-1,66; 10,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,59</t>
+          <t>-1,47; 4,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 6,5</t>
+          <t>-0,78; 6,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,74</t>
+          <t>0,12; 8,01</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,96; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,84; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 590,81</t>
+          <t>-63,16; 725,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 973,01</t>
+          <t>-44,9; 961,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 994,3</t>
+          <t>-34,42; 1148,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,63</t>
+          <t>-0,45; 4,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,74</t>
+          <t>-0,32; 4,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,27</t>
+          <t>0,81; 6,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 3,1</t>
+          <t>-3,52; 3,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,8</t>
+          <t>-4,66; 1,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 10,28</t>
+          <t>-1,07; 9,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,93</t>
+          <t>-1,36; 2,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,49</t>
+          <t>-1,85; 2,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,5</t>
+          <t>0,8; 7,01</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,22; —</t>
+          <t>-62,77; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,65; —</t>
+          <t>-7,54; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,72; 163,98</t>
+          <t>-68,29; 195,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,64; 124,97</t>
+          <t>-84,76; 104,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 440,0</t>
+          <t>-26,33; 424,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,25; 217,1</t>
+          <t>-47,73; 240,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 187,95</t>
+          <t>-57,62; 187,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 449,33</t>
+          <t>14,3; 468,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 3,69</t>
+          <t>-6,82; 3,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 3,52</t>
+          <t>-6,47; 3,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 11,12</t>
+          <t>-0,59; 11,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,79</t>
+          <t>-6,69; 3,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 0,54</t>
+          <t>-7,93; 1,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 6,56</t>
+          <t>-4,21; 6,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 1,94</t>
+          <t>-5,58; 1,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 0,94</t>
+          <t>-5,95; 0,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 7,53</t>
+          <t>-1,27; 6,96</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-91,0; 366,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,36; 287,31</t>
+          <t>-84,65; 321,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 671,85</t>
+          <t>-23,22; 689,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-83,05; 156,19</t>
+          <t>-80,63; 153,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,08; 221,22</t>
+          <t>-47,89; 290,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 78,72</t>
+          <t>-74,73; 73,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-82,61; 33,98</t>
+          <t>-79,62; 44,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 236,46</t>
+          <t>-18,49; 233,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,73; 11,88</t>
+          <t>0,27; 10,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,04</t>
+          <t>-1,19; 5,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,55; 14,03</t>
+          <t>2,82; 13,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,58</t>
+          <t>-2,22; 8,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 2,18</t>
+          <t>-5,53; 2,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,64; 15,57</t>
+          <t>0,69; 14,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,08; 7,19</t>
+          <t>0,12; 7,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,22</t>
+          <t>-2,64; 2,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,16; 11,86</t>
+          <t>3,22; 11,71</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-67,88; —</t>
+          <t>-70,48; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 1789,79</t>
+          <t>-16,84; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 1074,41</t>
+          <t>-32,64; 1087,29</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>83,55; 2006,35</t>
+          <t>45,25; 1736,38</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,84</t>
+          <t>-0,43; 2,75</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,6</t>
+          <t>-0,65; 2,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,33</t>
+          <t>1,68; 5,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,92</t>
+          <t>-1,66; 2,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,36</t>
+          <t>-2,91; 0,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,91</t>
+          <t>0,48; 5,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,75</t>
+          <t>-0,61; 1,77</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,01</t>
+          <t>-1,36; 0,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,69</t>
+          <t>1,7; 4,59</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 244,75</t>
+          <t>-22,97; 240,76</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 238,89</t>
+          <t>-30,41; 209,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>51,56; 465,58</t>
+          <t>56,7; 421,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 75,99</t>
+          <t>-37,9; 79,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 20,49</t>
+          <t>-66,11; 22,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,66; 192,41</t>
+          <t>8,16; 191,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 89,3</t>
+          <t>-19,65; 86,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 50,81</t>
+          <t>-41,27; 40,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>48,65; 212,94</t>
+          <t>52,3; 222,39</t>
         </is>
       </c>
     </row>
